--- a/education_forms/032_si_units_quiz--education_forms.xlsx
+++ b/education_forms/032_si_units_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>a/m</t>
+          <t>rad/s</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>A/m</t>
+          <t>rad/s</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>°c</t>
+          <t>v/m</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>V/m</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>rad/s</t>
+          <t>a·c/m</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>rad/s</t>
+          <t>A·C/m</t>
         </is>
       </c>
     </row>
@@ -1540,63 +1540,63 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>v/m</t>
+          <t>rad/m</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>V/m</t>
+          <t>rad/m</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>unit_symbols_choices</t>
+          <t>prefixes_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>a/m</t>
+          <t>mega</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>A/m</t>
+          <t>mega</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>unit_symbols_choices</t>
+          <t>prefixes_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>a·c/m</t>
+          <t>giga</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>A·C/m</t>
+          <t>giga</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>unit_symbols_choices</t>
+          <t>prefixes_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>rad/m</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>rad/m</t>
+          <t>micro</t>
         </is>
       </c>
     </row>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>mega</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>mega</t>
+          <t>kilo</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>giga</t>
+          <t>centi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>giga</t>
+          <t>centi</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mili</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mili</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>deci</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>deci</t>
         </is>
       </c>
     </row>
@@ -1676,63 +1676,63 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>centi</t>
+          <t>deca</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>centi</t>
+          <t>deca</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>prefixes_choices</t>
+          <t>derived_units2_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>mili</t>
+          <t>ampere</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mili</t>
+          <t>Ampere</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>prefixes_choices</t>
+          <t>derived_units2_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>deci</t>
+          <t>ampere_per_meter</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>deci</t>
+          <t>Ampere per Meter</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>prefixes_choices</t>
+          <t>derived_units2_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>deca</t>
+          <t>a/m</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>deca</t>
+          <t>A/m</t>
         </is>
       </c>
     </row>
@@ -1744,80 +1744,80 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ampere</t>
+          <t>a·m/m</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ampere</t>
+          <t>A·m/m</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>derived_units2_choices</t>
+          <t>base_symbols_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ampere_per_meter</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ampere per Meter</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>derived_units2_choices</t>
+          <t>base_symbols_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>a/m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>A/m</t>
+          <t>kg</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>derived_units2_choices</t>
+          <t>base_symbols_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>a/m</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>A/m</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>derived_units2_choices</t>
+          <t>base_symbols_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>a·m/m</t>
+          <t>kg/m</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>A·m/m</t>
+          <t>kg/m</t>
         </is>
       </c>
     </row>
@@ -1829,78 +1829,10 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>°c</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>base_symbols_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>base_symbols_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>base_symbols_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>kg/m</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>kg/m</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>base_symbols_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>°c</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
